--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>403</v>
+        <v>186</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="G3">
-        <v>401</v>
+        <v>185</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="E2">
         <v>45</v>
       </c>
       <c r="G2">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>75</v>
       </c>
       <c r="E3">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="H3">
         <v>426</v>
